--- a/artfynd/A 26731-2024 artfynd.xlsx
+++ b/artfynd/A 26731-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676003</v>
+        <v>118676007</v>
       </c>
       <c r="B2" t="n">
-        <v>91779</v>
+        <v>91405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741429</v>
+        <v>741351</v>
       </c>
       <c r="R2" t="n">
-        <v>7295696</v>
+        <v>7295697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676007</v>
+        <v>118676003</v>
       </c>
       <c r="B3" t="n">
-        <v>91405</v>
+        <v>91779</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741351</v>
+        <v>741429</v>
       </c>
       <c r="R3" t="n">
-        <v>7295697</v>
+        <v>7295696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676001</v>
+        <v>118676005</v>
       </c>
       <c r="B4" t="n">
-        <v>91791</v>
+        <v>91825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>232140</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741371</v>
+        <v>741422</v>
       </c>
       <c r="R4" t="n">
-        <v>7295662</v>
+        <v>7295686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676004</v>
+        <v>118676001</v>
       </c>
       <c r="B6" t="n">
-        <v>89154</v>
+        <v>91791</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1593</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741431</v>
+        <v>741371</v>
       </c>
       <c r="R6" t="n">
-        <v>7295694</v>
+        <v>7295662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676005</v>
+        <v>118676006</v>
       </c>
       <c r="B7" t="n">
-        <v>91825</v>
+        <v>91771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>232140</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676006</v>
+        <v>118676004</v>
       </c>
       <c r="B8" t="n">
-        <v>91771</v>
+        <v>89154</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>1593</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741422</v>
+        <v>741431</v>
       </c>
       <c r="R8" t="n">
-        <v>7295686</v>
+        <v>7295694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26731-2024 artfynd.xlsx
+++ b/artfynd/A 26731-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676003</v>
+        <v>118676005</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>91825</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741429</v>
+        <v>741422</v>
       </c>
       <c r="R3" t="n">
-        <v>7295696</v>
+        <v>7295686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676005</v>
+        <v>118676003</v>
       </c>
       <c r="B4" t="n">
-        <v>91825</v>
+        <v>91779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741422</v>
+        <v>741429</v>
       </c>
       <c r="R4" t="n">
-        <v>7295686</v>
+        <v>7295696</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 26731-2024 artfynd.xlsx
+++ b/artfynd/A 26731-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676007</v>
+        <v>118676004</v>
       </c>
       <c r="B2" t="n">
-        <v>91405</v>
+        <v>89154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741351</v>
+        <v>741431</v>
       </c>
       <c r="R2" t="n">
-        <v>7295697</v>
+        <v>7295694</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676005</v>
+        <v>118676006</v>
       </c>
       <c r="B3" t="n">
-        <v>91825</v>
+        <v>91771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>232140</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676003</v>
+        <v>118676005</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>91825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741429</v>
+        <v>741422</v>
       </c>
       <c r="R4" t="n">
-        <v>7295696</v>
+        <v>7295686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676002</v>
+        <v>118676003</v>
       </c>
       <c r="B5" t="n">
-        <v>91822</v>
+        <v>91779</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676001</v>
+        <v>118676002</v>
       </c>
       <c r="B6" t="n">
-        <v>91791</v>
+        <v>91822</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741371</v>
+        <v>741429</v>
       </c>
       <c r="R6" t="n">
-        <v>7295662</v>
+        <v>7295696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676006</v>
+        <v>118676007</v>
       </c>
       <c r="B7" t="n">
-        <v>91771</v>
+        <v>91405</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741422</v>
+        <v>741351</v>
       </c>
       <c r="R7" t="n">
-        <v>7295686</v>
+        <v>7295697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676004</v>
+        <v>118676001</v>
       </c>
       <c r="B8" t="n">
-        <v>89154</v>
+        <v>91791</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1593</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741431</v>
+        <v>741371</v>
       </c>
       <c r="R8" t="n">
-        <v>7295694</v>
+        <v>7295662</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26731-2024 artfynd.xlsx
+++ b/artfynd/A 26731-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676004</v>
+        <v>118676006</v>
       </c>
       <c r="B2" t="n">
-        <v>89154</v>
+        <v>91778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1593</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741431</v>
+        <v>741422</v>
       </c>
       <c r="R2" t="n">
-        <v>7295694</v>
+        <v>7295686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676006</v>
+        <v>118676003</v>
       </c>
       <c r="B3" t="n">
-        <v>91771</v>
+        <v>91786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741422</v>
+        <v>741429</v>
       </c>
       <c r="R3" t="n">
-        <v>7295686</v>
+        <v>7295696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676005</v>
+        <v>118676007</v>
       </c>
       <c r="B4" t="n">
-        <v>91825</v>
+        <v>91412</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>232140</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741422</v>
+        <v>741351</v>
       </c>
       <c r="R4" t="n">
-        <v>7295686</v>
+        <v>7295697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676003</v>
+        <v>118676001</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>91798</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741429</v>
+        <v>741371</v>
       </c>
       <c r="R5" t="n">
-        <v>7295696</v>
+        <v>7295662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676002</v>
+        <v>118676004</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
+        <v>89161</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>1593</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741429</v>
+        <v>741431</v>
       </c>
       <c r="R6" t="n">
-        <v>7295696</v>
+        <v>7295694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676007</v>
+        <v>118676002</v>
       </c>
       <c r="B7" t="n">
-        <v>91405</v>
+        <v>91829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4745</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741351</v>
+        <v>741429</v>
       </c>
       <c r="R7" t="n">
-        <v>7295697</v>
+        <v>7295696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676001</v>
+        <v>118676005</v>
       </c>
       <c r="B8" t="n">
-        <v>91791</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>232140</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741371</v>
+        <v>741422</v>
       </c>
       <c r="R8" t="n">
-        <v>7295662</v>
+        <v>7295686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26731-2024 artfynd.xlsx
+++ b/artfynd/A 26731-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676003</v>
+        <v>118676005</v>
       </c>
       <c r="B3" t="n">
-        <v>91786</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741429</v>
+        <v>741422</v>
       </c>
       <c r="R3" t="n">
-        <v>7295696</v>
+        <v>7295686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676007</v>
+        <v>118676004</v>
       </c>
       <c r="B4" t="n">
-        <v>91412</v>
+        <v>89161</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>1593</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741351</v>
+        <v>741431</v>
       </c>
       <c r="R4" t="n">
-        <v>7295697</v>
+        <v>7295694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676001</v>
+        <v>118676007</v>
       </c>
       <c r="B5" t="n">
-        <v>91798</v>
+        <v>91412</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741371</v>
+        <v>741351</v>
       </c>
       <c r="R5" t="n">
-        <v>7295662</v>
+        <v>7295697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676004</v>
+        <v>118676001</v>
       </c>
       <c r="B6" t="n">
-        <v>89161</v>
+        <v>91798</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1593</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741431</v>
+        <v>741371</v>
       </c>
       <c r="R6" t="n">
-        <v>7295694</v>
+        <v>7295662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676002</v>
+        <v>118676003</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>91786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676005</v>
+        <v>118676002</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91829</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232140</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741422</v>
+        <v>741429</v>
       </c>
       <c r="R8" t="n">
-        <v>7295686</v>
+        <v>7295696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26731-2024 artfynd.xlsx
+++ b/artfynd/A 26731-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676007</v>
+        <v>118676004</v>
       </c>
       <c r="B2" t="n">
-        <v>91414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741351</v>
+        <v>741431</v>
       </c>
       <c r="R2" t="n">
-        <v>7295697</v>
+        <v>7295694</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676005</v>
+        <v>118676006</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>232140</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -900,16 +890,11 @@
         <v>118676003</v>
       </c>
       <c r="B4" t="n">
-        <v>91791</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1011,16 +996,11 @@
         <v>118676001</v>
       </c>
       <c r="B5" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676004</v>
+        <v>118676007</v>
       </c>
       <c r="B6" t="n">
-        <v>89163</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1593</v>
+        <v>4745</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741431</v>
+        <v>741351</v>
       </c>
       <c r="R6" t="n">
-        <v>7295694</v>
+        <v>7295697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,12 +1208,7 @@
         <v>118676002</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1341,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676006</v>
+        <v>118676005</v>
       </c>
       <c r="B8" t="n">
-        <v>91783</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>232140</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/artfynd/A 26731-2024 artfynd.xlsx
+++ b/artfynd/A 26731-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676004</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676006</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676007</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676002</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676005</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>